--- a/public/uploaders/ADVISORY-CLASS-UPLOADER-SHS.xlsx
+++ b/public/uploaders/ADVISORY-CLASS-UPLOADER-SHS.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RBIS07\Desktop\Systems\System Files\STARS\Uploader\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\var\www\laravel\stars\public\uploaders\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCEB8DE-FDC6-48C8-8FDF-4A18DC6DC8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F676896F-57E3-4709-A7F8-FB94BF860AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A960304A-B4A2-4A46-A81D-876F4C2E5A3F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A960304A-B4A2-4A46-A81D-876F4C2E5A3F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ENCODE here" sheetId="1" r:id="rId1"/>
     <sheet name="REFERENCE " sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -628,10 +628,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -643,7 +642,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -682,9 +680,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -722,7 +720,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -828,7 +826,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -970,7 +968,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -981,14 +979,14 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.77734375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.6640625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="31.44140625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="58" style="8" customWidth="1"/>
-    <col min="7" max="7" width="34.5546875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.77734375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="58" style="7" customWidth="1"/>
+    <col min="7" max="7" width="34.5546875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.21875" customWidth="1"/>
     <col min="11" max="11" width="32.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
@@ -998,92 +996,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1138,46 +1136,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="16"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1185,19 +1183,19 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1205,1223 +1203,963 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
       <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
       <c r="C8" s="1">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>7</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
       <c r="C10" s="1">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
       <c r="C11" s="1">
         <v>9</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="1">
         <v>9</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
       <c r="C12" s="1">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
       <c r="C13" s="1">
         <v>11</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="1">
         <v>11</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
       <c r="C14" s="1">
         <v>12</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="1">
         <v>12</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
       <c r="C15" s="1">
         <v>13</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="1">
         <v>13</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
       <c r="C16" s="1">
         <v>14</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="1">
         <v>14</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>15</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="1">
         <v>15</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
       <c r="E18" s="1">
         <v>16</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
       <c r="E19" s="1">
         <v>17</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
       <c r="E20" s="1">
         <v>18</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
       <c r="E21" s="1">
         <v>19</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
       <c r="E22" s="1">
         <v>20</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
       <c r="E23" s="1">
         <v>21</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
       <c r="E24" s="1">
         <v>22</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
       <c r="E25" s="1">
         <v>23</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
       <c r="E26" s="1">
         <v>24</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
       <c r="E27" s="1">
         <v>25</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
       <c r="E28" s="1">
         <v>26</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
       <c r="E29" s="1">
         <v>27</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
       <c r="E30" s="1">
         <v>28</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
       <c r="E31" s="1">
         <v>29</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
       <c r="E32" s="1">
         <v>30</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
       <c r="E33" s="1">
         <v>31</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
       <c r="E34" s="1">
         <v>32</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
       <c r="E35" s="1">
         <v>33</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
       <c r="E36" s="1">
         <v>34</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
       <c r="E37" s="1">
         <v>35</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
       <c r="E38" s="1">
         <v>36</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
       <c r="E39" s="1">
         <v>37</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
       <c r="E40" s="1">
         <v>38</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
       <c r="E41" s="1">
         <v>39</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
       <c r="E42" s="1">
         <v>40</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
       <c r="E43" s="1">
         <v>41</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
       <c r="E44" s="1">
         <v>42</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
       <c r="E45" s="1">
         <v>43</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
       <c r="E46" s="1">
         <v>44</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
       <c r="E47" s="1">
         <v>45</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
       <c r="E48" s="1">
         <v>46</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
       <c r="E49" s="1">
         <v>47</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
       <c r="E50" s="1">
         <v>48</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
       <c r="E51" s="1">
         <v>49</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
       <c r="E52" s="1">
         <v>50</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
       <c r="E53" s="1">
         <v>51</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
       <c r="E54" s="1">
         <v>52</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
       <c r="E55" s="1">
         <v>53</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
       <c r="E56" s="1">
         <v>54</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
       <c r="E57" s="1">
         <v>55</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
       <c r="E58" s="1">
         <v>56</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
       <c r="E59" s="1">
         <v>57</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
       <c r="E60" s="1">
         <v>58</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
       <c r="E61" s="1">
         <v>59</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
       <c r="E62" s="1">
         <v>60</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
       <c r="E63" s="1">
         <v>61</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
       <c r="E64" s="1">
         <v>62</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
       <c r="E65" s="1">
         <v>63</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
       <c r="E66" s="1">
         <v>64</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
       <c r="E67" s="1">
         <v>65</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
       <c r="E68" s="1">
         <v>66</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
       <c r="E69" s="1">
         <v>67</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
       <c r="E70" s="1">
         <v>68</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
       <c r="E71" s="1">
         <v>69</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
       <c r="E72" s="1">
         <v>70</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
       <c r="E73" s="1">
         <v>71</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
       <c r="E74" s="1">
         <v>72</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
       <c r="E75" s="1">
         <v>73</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="2" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
       <c r="E76" s="1">
         <v>74</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
       <c r="E77" s="1">
         <v>75</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
       <c r="E78" s="1">
         <v>76</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
       <c r="E79" s="1">
         <v>77</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
       <c r="E80" s="1">
         <v>78</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
       <c r="E81" s="1">
         <v>79</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
       <c r="E82" s="1">
         <v>80</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
       <c r="E83" s="1">
         <v>81</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="2" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
       <c r="E84" s="1">
         <v>82</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
       <c r="E85" s="1">
         <v>83</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
       <c r="E86" s="1">
         <v>84</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
       <c r="E87" s="1">
         <v>85</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="2" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
       <c r="E88" s="1">
         <v>86</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
       <c r="E89" s="1">
         <v>87</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
       <c r="E90" s="1">
         <v>88</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
       <c r="E91" s="1">
         <v>89</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
       <c r="E92" s="1">
         <v>90</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
       <c r="E93" s="1">
         <v>91</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="2" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
       <c r="E94" s="1">
         <v>92</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
       <c r="E95" s="1">
         <v>93</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
       <c r="E96" s="1">
         <v>94</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
       <c r="E97" s="1">
         <v>95</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
       <c r="E98" s="1">
         <v>96</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
       <c r="E99" s="1">
         <v>97</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="2" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
       <c r="E100" s="1">
         <v>98</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="4"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="4">
+      <c r="A101" s="3"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="3">
         <v>99</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F101" s="5" t="s">
         <v>122</v>
       </c>
     </row>
